--- a/Cópia de Preços Tabela atual.xlsx
+++ b/Cópia de Preços Tabela atual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jorge Soares\Desktop\APP2\dist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{143DD011-3922-4CFF-9514-A83224B180BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8919383-6567-4C8F-AC6A-311D9854643C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{239B5EC5-0046-43A7-8F2E-487CD1E3F215}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="302">
   <si>
     <t>DESCRIÇAO</t>
   </si>
@@ -948,6 +948,15 @@
   <si>
     <t>ARP 142</t>
   </si>
+  <si>
+    <t>VALORES ATUAIS JANEIRO 2025</t>
+  </si>
+  <si>
+    <t>UNID</t>
+  </si>
+  <si>
+    <t>DESCRIÇÃO</t>
+  </si>
 </sst>
 </file>
 
@@ -958,7 +967,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-816]_-;\-* #,##0.00\ [$€-816]_-;_-* &quot;-&quot;??\ [$€-816]_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1003,6 +1012,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1052,7 +1069,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1075,6 +1092,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1083,7 +1126,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1164,6 +1207,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4441,21 +4490,21 @@
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="2" max="2" width="105.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="44" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>1</v>
+      <c r="B1" s="43" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>300</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>2</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
